--- a/CNAE_2.3_NIB_HS.xlsx
+++ b/CNAE_2.3_NIB_HS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre.carmona\Desktop\Projetos\1. Projetos em R\2. De_para_CNAE_SNCT_ISIC_p&amp;dOCDE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre.carmona\Desktop\Projetos\1. Projetos em R\2. De_para CNAE x SNCT x ISIC x P&amp;D_OCDE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B77E8CC-E3D2-42EB-A253-FFBEB3EB547C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0F66E67-3753-4614-9FFE-53016DFA553D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{301B068B-BAB9-4CEE-A666-E9697B4BCA4F}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="398">
   <si>
     <t>Número da Missão</t>
   </si>
@@ -2318,7 +2318,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88C6ECC4-09C3-4F88-8DCB-0D6FDF8F1FA5}">
-  <dimension ref="A1:Q126"/>
+  <dimension ref="A1:N126"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23.42578125" customWidth="1"/>
@@ -2776,7 +2776,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
         <v>74</v>
       </c>
@@ -2802,7 +2802,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E18">
         <v>1313800</v>
       </c>
@@ -2825,7 +2825,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E19">
         <v>3292201</v>
       </c>
@@ -2854,7 +2854,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2</v>
       </c>
@@ -2892,7 +2892,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E21">
         <v>2121102</v>
       </c>
@@ -2918,7 +2918,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E22">
         <v>2121103</v>
       </c>
@@ -2944,7 +2944,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E23">
         <v>2110600</v>
       </c>
@@ -2970,7 +2970,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C24" t="s">
         <v>98</v>
       </c>
@@ -3002,7 +3002,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C25" t="s">
         <v>102</v>
       </c>
@@ -3013,7 +3013,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E26">
         <v>2660400</v>
       </c>
@@ -3039,7 +3039,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E27">
         <v>3250701</v>
       </c>
@@ -3064,11 +3064,8 @@
       <c r="N27" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="Q27" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E28">
         <v>3250702</v>
       </c>
@@ -3093,11 +3090,8 @@
       <c r="N28" t="s">
         <v>112</v>
       </c>
-      <c r="O28" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E29">
         <v>3250705</v>
       </c>
@@ -3123,7 +3117,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>3</v>
       </c>
@@ -3161,7 +3155,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E31">
         <v>2710403</v>
       </c>
